--- a/协作/22-集成记录.xlsx
+++ b/协作/22-集成记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -557,6 +557,48 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>未部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>77fb43c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>APPROVE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>人工核对</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>未部署</t>
         </is>

--- a/协作/22-集成记录.xlsx
+++ b/协作/22-集成记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -599,6 +599,48 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>未部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0436ca2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>APPROVE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>人工核对</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:05:00 +08:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>未部署</t>
         </is>

--- a/协作/22-集成记录.xlsx
+++ b/协作/22-集成记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -641,6 +641,48 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>未部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cbe8fbe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>APPROVE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>人工核对</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>未部署</t>
         </is>

--- a/协作/22-集成记录.xlsx
+++ b/协作/22-集成记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -683,6 +683,48 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>未部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7c4760d</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>APPROVE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>人工核对</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>未部署</t>
         </is>

--- a/协作/22-集成记录.xlsx
+++ b/协作/22-集成记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -725,6 +725,48 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>未部署</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ba1410d</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>APPROVE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>人工核对</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:55:00 +08:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>未部署</t>
         </is>
